--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -657,7 +657,7 @@
         <v>0.04424999999999998</v>
       </c>
       <c r="H5">
-        <v>0.0277211570918228</v>
+        <v>0.02772115709182282</v>
       </c>
       <c r="I5">
         <v>0.01249222169102884</v>
@@ -678,7 +678,7 @@
         <v>0.02859347826086958</v>
       </c>
       <c r="O5">
-        <v>0.01206463535269239</v>
+        <v>0.01206463535269242</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
@@ -939,7 +939,7 @@
         <v>0.05200000000000002</v>
       </c>
       <c r="H11">
-        <v>0.04327339885162035</v>
+        <v>0.04327339885162032</v>
       </c>
       <c r="I11">
         <v>0.02820962773999661</v>
@@ -960,7 +960,7 @@
         <v>0.04500000000000004</v>
       </c>
       <c r="O11">
-        <v>0.03627339885162037</v>
+        <v>0.03627339885162034</v>
       </c>
       <c r="P11" t="b">
         <v>1</v>
@@ -1080,7 +1080,7 @@
         <v>0.01862500000000003</v>
       </c>
       <c r="H14">
-        <v>0.008256875250248846</v>
+        <v>0.008256875250248874</v>
       </c>
       <c r="I14">
         <v>0.01001663639923409</v>
@@ -1101,7 +1101,7 @@
         <v>0.0172500000000001</v>
       </c>
       <c r="O14">
-        <v>0.006881875250248914</v>
+        <v>0.006881875250248942</v>
       </c>
       <c r="P14" t="b">
         <v>1</v>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="19">
   <si>
     <t>Outer Test Year</t>
   </si>
@@ -70,16 +70,7 @@
     <t>Popular Vote</t>
   </si>
   <si>
-    <t>House Buckets</t>
-  </si>
-  <si>
-    <t>Senate Buckets</t>
-  </si>
-  <si>
     <t>D-R popular vote margin MAE (percentage points)</t>
-  </si>
-  <si>
-    <t>Mean target MAE in native units</t>
   </si>
 </sst>
 </file>
@@ -437,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:17">
@@ -516,10 +507,10 @@
         <v>0.04824999999999999</v>
       </c>
       <c r="H2">
-        <v>0.02831546786444183</v>
+        <v>0.02728243835797947</v>
       </c>
       <c r="I2">
-        <v>0.01990148610361578</v>
+        <v>0.01891389104090235</v>
       </c>
       <c r="J2">
         <v>0.02029126213592225</v>
@@ -528,7 +519,7 @@
         <v>0.02029126213592225</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -537,7 +528,7 @@
         <v>0.02795873786407774</v>
       </c>
       <c r="O2">
-        <v>0.008024205728519584</v>
+        <v>0.006991176222057222</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -548,40 +539,49 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
+        <v>2.043919732157621</v>
+      </c>
+      <c r="E3">
+        <v>0.0156565217391304</v>
+      </c>
+      <c r="F3">
+        <v>-2.028263210418491</v>
+      </c>
+      <c r="G3">
+        <v>0.04424999999999998</v>
+      </c>
+      <c r="H3">
+        <v>0.0245124324816314</v>
+      </c>
+      <c r="I3">
+        <v>0.01871874414125238</v>
+      </c>
+      <c r="J3">
+        <v>0.0156565217391304</v>
+      </c>
+      <c r="K3">
+        <v>0.0156565217391304</v>
+      </c>
+      <c r="L3" t="s">
         <v>18</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <v>6.48365908322933</v>
-      </c>
-      <c r="E3">
-        <v>2.551785240009931</v>
-      </c>
-      <c r="F3">
-        <v>-3.9318738432194</v>
-      </c>
-      <c r="G3">
-        <v>4.78125</v>
-      </c>
-      <c r="H3">
-        <v>2.753676578645634</v>
-      </c>
-      <c r="I3">
-        <v>2.551785240009931</v>
-      </c>
-      <c r="L3" t="s">
-        <v>21</v>
+      <c r="M3">
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.229464759990069</v>
+        <v>0.02859347826086958</v>
       </c>
       <c r="O3">
-        <v>0.2018913386357033</v>
+        <v>0.008855910742501</v>
       </c>
       <c r="P3" t="b">
         <v>1</v>
@@ -592,40 +592,49 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4">
-        <v>2006</v>
+        <v>2014</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4">
-        <v>1.132854998160983</v>
+        <v>2.063735477916174</v>
       </c>
       <c r="E4">
-        <v>0.9615308633365063</v>
+        <v>0.01536824324324321</v>
       </c>
       <c r="F4">
-        <v>-0.1713241348244765</v>
+        <v>-2.048367234672931</v>
       </c>
       <c r="G4">
-        <v>1.453125</v>
+        <v>0.03737500000000002</v>
       </c>
       <c r="H4">
-        <v>1.074411743411713</v>
+        <v>0.02873619166922875</v>
       </c>
       <c r="I4">
-        <v>0.9615308633365064</v>
+        <v>0.02522042241834396</v>
+      </c>
+      <c r="J4">
+        <v>0.01536824324324321</v>
+      </c>
+      <c r="K4">
+        <v>0.01536824324324321</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>18</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>0.4915941366634937</v>
+        <v>0.02200675675675681</v>
       </c>
       <c r="O4">
-        <v>0.1128808800752068</v>
+        <v>0.01336794842598554</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>
@@ -636,7 +645,7 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -645,40 +654,40 @@
         <v>9</v>
       </c>
       <c r="D5">
-        <v>2.043919732157621</v>
+        <v>2.578312672275927</v>
       </c>
       <c r="E5">
-        <v>0.0156565217391304</v>
+        <v>0.006999999999999978</v>
       </c>
       <c r="F5">
-        <v>-2.028263210418491</v>
+        <v>-2.571312672275927</v>
       </c>
       <c r="G5">
-        <v>0.04424999999999998</v>
+        <v>0.05200000000000002</v>
       </c>
       <c r="H5">
-        <v>0.02772115709182282</v>
+        <v>0.04082777272570118</v>
       </c>
       <c r="I5">
-        <v>0.01249222169102884</v>
+        <v>0.04354401548334155</v>
       </c>
       <c r="J5">
-        <v>0.0156565217391304</v>
+        <v>0.006999999999999978</v>
       </c>
       <c r="K5">
-        <v>0.0156565217391304</v>
+        <v>0.006999999999999978</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5">
-        <v>0.02859347826086958</v>
+        <v>0.04500000000000004</v>
       </c>
       <c r="O5">
-        <v>0.01206463535269242</v>
+        <v>0.0338277727257012</v>
       </c>
       <c r="P5" t="b">
         <v>1</v>
@@ -689,513 +698,55 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>2.799367742338258</v>
+      </c>
+      <c r="E6">
+        <v>0.001374999999999932</v>
+      </c>
+      <c r="F6">
+        <v>-2.797992742338258</v>
+      </c>
+      <c r="G6">
+        <v>0.01862500000000003</v>
+      </c>
+      <c r="H6">
+        <v>0.002187908649066761</v>
+      </c>
+      <c r="I6">
+        <v>0.005372069085689518</v>
+      </c>
+      <c r="J6">
+        <v>0.001374999999999932</v>
+      </c>
+      <c r="K6">
+        <v>0.001374999999999932</v>
+      </c>
+      <c r="L6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6">
-        <v>4.452517519892867</v>
-      </c>
-      <c r="E6">
-        <v>7.349523097808222</v>
-      </c>
-      <c r="F6">
-        <v>2.897005577915355</v>
-      </c>
-      <c r="G6">
-        <v>8.9375</v>
-      </c>
-      <c r="H6">
-        <v>8.189048875432858</v>
-      </c>
-      <c r="I6">
-        <v>7.349523097808221</v>
-      </c>
-      <c r="L6" t="s">
-        <v>21</v>
+      <c r="M6">
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>1.587976902191778</v>
+        <v>0.0172500000000001</v>
       </c>
       <c r="O6">
-        <v>0.8395257776246368</v>
+        <v>0.0008129086490668291</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17">
-      <c r="A7">
-        <v>2010</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7">
-        <v>1.14891432916458</v>
-      </c>
-      <c r="E7">
-        <v>1.006504336393452</v>
-      </c>
-      <c r="F7">
-        <v>-0.1424099927711282</v>
-      </c>
-      <c r="G7">
-        <v>1.359375</v>
-      </c>
-      <c r="H7">
-        <v>1.042561047529763</v>
-      </c>
-      <c r="I7">
-        <v>1.006504336393452</v>
-      </c>
-      <c r="L7" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7">
-        <v>0.3528706636065484</v>
-      </c>
-      <c r="O7">
-        <v>0.03605671113631126</v>
-      </c>
-      <c r="P7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17">
-      <c r="A8">
-        <v>2014</v>
-      </c>
-      <c r="B8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>2.063735477916174</v>
-      </c>
-      <c r="E8">
-        <v>0.01536824324324321</v>
-      </c>
-      <c r="F8">
-        <v>-2.048367234672931</v>
-      </c>
-      <c r="G8">
-        <v>0.03737500000000002</v>
-      </c>
-      <c r="H8">
-        <v>0.02427269038993915</v>
-      </c>
-      <c r="I8">
-        <v>0.0110818744326957</v>
-      </c>
-      <c r="J8">
-        <v>0.01536824324324321</v>
-      </c>
-      <c r="K8">
-        <v>0.01536824324324321</v>
-      </c>
-      <c r="L8" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0.02200675675675681</v>
-      </c>
-      <c r="O8">
-        <v>0.008904447146695943</v>
-      </c>
-      <c r="P8" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17">
-      <c r="A9">
-        <v>2014</v>
-      </c>
-      <c r="B9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9">
-        <v>4.628669125976737</v>
-      </c>
-      <c r="E9">
-        <v>6.071601107835621</v>
-      </c>
-      <c r="F9">
-        <v>1.442931981858884</v>
-      </c>
-      <c r="G9">
-        <v>6.34375</v>
-      </c>
-      <c r="H9">
-        <v>5.726539617295953</v>
-      </c>
-      <c r="I9">
-        <v>6.071601107835621</v>
-      </c>
-      <c r="L9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N9">
-        <v>0.2721488921643793</v>
-      </c>
-      <c r="O9">
-        <v>-0.3450614905396678</v>
-      </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17">
-      <c r="A10">
-        <v>2014</v>
-      </c>
-      <c r="B10" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>1.023134447310966</v>
-      </c>
-      <c r="E10">
-        <v>0.7745227488775028</v>
-      </c>
-      <c r="F10">
-        <v>-0.248611698433463</v>
-      </c>
-      <c r="G10">
-        <v>1.09375</v>
-      </c>
-      <c r="H10">
-        <v>0.8529216245943888</v>
-      </c>
-      <c r="I10">
-        <v>0.7745227488775027</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10">
-        <v>0.3192272511224972</v>
-      </c>
-      <c r="O10">
-        <v>0.07839887571688597</v>
-      </c>
-      <c r="P10" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17">
-      <c r="A11">
-        <v>2018</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D11">
-        <v>2.578312672275927</v>
-      </c>
-      <c r="E11">
-        <v>0.006999999999999978</v>
-      </c>
-      <c r="F11">
-        <v>-2.571312672275927</v>
-      </c>
-      <c r="G11">
-        <v>0.05200000000000002</v>
-      </c>
-      <c r="H11">
-        <v>0.04327339885162032</v>
-      </c>
-      <c r="I11">
-        <v>0.02820962773999661</v>
-      </c>
-      <c r="J11">
-        <v>0.006999999999999978</v>
-      </c>
-      <c r="K11">
-        <v>0.006999999999999978</v>
-      </c>
-      <c r="L11" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0.04500000000000004</v>
-      </c>
-      <c r="O11">
-        <v>0.03627339885162034</v>
-      </c>
-      <c r="P11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17">
-      <c r="A12">
-        <v>2018</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12">
-        <v>5.505856602954813</v>
-      </c>
-      <c r="E12">
-        <v>7.259981095064756</v>
-      </c>
-      <c r="F12">
-        <v>1.754124492109943</v>
-      </c>
-      <c r="G12">
-        <v>9.28125</v>
-      </c>
-      <c r="H12">
-        <v>8.360830942999556</v>
-      </c>
-      <c r="I12">
-        <v>7.259981095064755</v>
-      </c>
-      <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12">
-        <v>2.021268904935244</v>
-      </c>
-      <c r="O12">
-        <v>1.1008498479348</v>
-      </c>
-      <c r="P12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17">
-      <c r="A13">
-        <v>2018</v>
-      </c>
-      <c r="B13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13">
-        <v>1.137647266588851</v>
-      </c>
-      <c r="E13">
-        <v>1.30779306486022</v>
-      </c>
-      <c r="F13">
-        <v>0.1701457982713688</v>
-      </c>
-      <c r="G13">
-        <v>1.546875</v>
-      </c>
-      <c r="H13">
-        <v>1.409450249532496</v>
-      </c>
-      <c r="I13">
-        <v>1.307793064860219</v>
-      </c>
-      <c r="L13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13">
-        <v>0.2390819351397804</v>
-      </c>
-      <c r="O13">
-        <v>0.1016571846722765</v>
-      </c>
-      <c r="P13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17">
-      <c r="A14">
-        <v>2022</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14">
-        <v>2.799367742338258</v>
-      </c>
-      <c r="E14">
-        <v>0.001374999999999932</v>
-      </c>
-      <c r="F14">
-        <v>-2.797992742338258</v>
-      </c>
-      <c r="G14">
-        <v>0.01862500000000003</v>
-      </c>
-      <c r="H14">
-        <v>0.008256875250248874</v>
-      </c>
-      <c r="I14">
-        <v>0.01001663639923409</v>
-      </c>
-      <c r="J14">
-        <v>0.001374999999999932</v>
-      </c>
-      <c r="K14">
-        <v>0.001374999999999932</v>
-      </c>
-      <c r="L14" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0.0172500000000001</v>
-      </c>
-      <c r="O14">
-        <v>0.006881875250248942</v>
-      </c>
-      <c r="P14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17">
-      <c r="A15">
-        <v>2022</v>
-      </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <v>6.227766123397645</v>
-      </c>
-      <c r="E15">
-        <v>3.004590444317271</v>
-      </c>
-      <c r="F15">
-        <v>-3.223175679080374</v>
-      </c>
-      <c r="G15">
-        <v>2.65625</v>
-      </c>
-      <c r="H15">
-        <v>3.113447840591852</v>
-      </c>
-      <c r="I15">
-        <v>3.004590444317271</v>
-      </c>
-      <c r="L15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15">
-        <v>-0.3483404443172713</v>
-      </c>
-      <c r="O15">
-        <v>0.1088573962745807</v>
-      </c>
-      <c r="P15" t="b">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17">
-      <c r="A16">
-        <v>2022</v>
-      </c>
-      <c r="B16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16">
-        <v>0.998493356179856</v>
-      </c>
-      <c r="E16">
-        <v>1.141729553470553</v>
-      </c>
-      <c r="F16">
-        <v>0.1432361972906967</v>
-      </c>
-      <c r="G16">
-        <v>1.234375</v>
-      </c>
-      <c r="H16">
-        <v>1.122296082584525</v>
-      </c>
-      <c r="I16">
-        <v>1.141729553470553</v>
-      </c>
-      <c r="L16" t="s">
-        <v>21</v>
-      </c>
-      <c r="N16">
-        <v>0.09264544652944728</v>
-      </c>
-      <c r="O16">
-        <v>-0.01943347088602754</v>
-      </c>
-      <c r="P16" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -507,7 +507,7 @@
         <v>0.04824999999999999</v>
       </c>
       <c r="H2">
-        <v>0.02728243835797947</v>
+        <v>0.02728243835797942</v>
       </c>
       <c r="I2">
         <v>0.01891389104090235</v>
@@ -528,7 +528,7 @@
         <v>0.02795873786407774</v>
       </c>
       <c r="O2">
-        <v>0.006991176222057222</v>
+        <v>0.006991176222057166</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -507,7 +507,7 @@
         <v>0.04824999999999999</v>
       </c>
       <c r="H2">
-        <v>0.02728243835797942</v>
+        <v>0.02728243835797947</v>
       </c>
       <c r="I2">
         <v>0.01891389104090235</v>
@@ -528,7 +528,7 @@
         <v>0.02795873786407774</v>
       </c>
       <c r="O2">
-        <v>0.006991176222057166</v>
+        <v>0.006991176222057222</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -613,7 +613,7 @@
         <v>0.03737500000000002</v>
       </c>
       <c r="H4">
-        <v>0.02873619166922875</v>
+        <v>0.02873619166922872</v>
       </c>
       <c r="I4">
         <v>0.02522042241834396</v>
@@ -634,7 +634,7 @@
         <v>0.02200675675675681</v>
       </c>
       <c r="O4">
-        <v>0.01336794842598554</v>
+        <v>0.01336794842598552</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -613,7 +613,7 @@
         <v>0.03737500000000002</v>
       </c>
       <c r="H4">
-        <v>0.02873619166922872</v>
+        <v>0.02873619166922875</v>
       </c>
       <c r="I4">
         <v>0.02522042241834396</v>
@@ -634,7 +634,7 @@
         <v>0.02200675675675681</v>
       </c>
       <c r="O4">
-        <v>0.01336794842598552</v>
+        <v>0.01336794842598554</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -507,7 +507,7 @@
         <v>0.04824999999999999</v>
       </c>
       <c r="H2">
-        <v>0.02728243835797947</v>
+        <v>0.02728243835797942</v>
       </c>
       <c r="I2">
         <v>0.01891389104090235</v>
@@ -528,7 +528,7 @@
         <v>0.02795873786407774</v>
       </c>
       <c r="O2">
-        <v>0.006991176222057222</v>
+        <v>0.006991176222057166</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -719,7 +719,7 @@
         <v>0.01862500000000003</v>
       </c>
       <c r="H6">
-        <v>0.002187908649066761</v>
+        <v>0.002187908649066789</v>
       </c>
       <c r="I6">
         <v>0.005372069085689518</v>
@@ -740,7 +740,7 @@
         <v>0.0172500000000001</v>
       </c>
       <c r="O6">
-        <v>0.0008129086490668291</v>
+        <v>0.0008129086490668569</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -719,7 +719,7 @@
         <v>0.01862500000000003</v>
       </c>
       <c r="H6">
-        <v>0.002187908649066789</v>
+        <v>0.002187908649066761</v>
       </c>
       <c r="I6">
         <v>0.005372069085689518</v>
@@ -740,7 +740,7 @@
         <v>0.0172500000000001</v>
       </c>
       <c r="O6">
-        <v>0.0008129086490668569</v>
+        <v>0.0008129086490668291</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -507,7 +507,7 @@
         <v>0.04824999999999999</v>
       </c>
       <c r="H2">
-        <v>0.02728243835797942</v>
+        <v>0.02728243835797947</v>
       </c>
       <c r="I2">
         <v>0.01891389104090235</v>
@@ -528,7 +528,7 @@
         <v>0.02795873786407774</v>
       </c>
       <c r="O2">
-        <v>0.006991176222057166</v>
+        <v>0.006991176222057222</v>
       </c>
       <c r="P2" t="b">
         <v>1</v>
@@ -613,7 +613,7 @@
         <v>0.03737500000000002</v>
       </c>
       <c r="H4">
-        <v>0.02873619166922872</v>
+        <v>0.02873619166922875</v>
       </c>
       <c r="I4">
         <v>0.02522042241834396</v>
@@ -634,7 +634,7 @@
         <v>0.02200675675675681</v>
       </c>
       <c r="O4">
-        <v>0.01336794842598552</v>
+        <v>0.01336794842598554</v>
       </c>
       <c r="P4" t="b">
         <v>1</v>

--- a/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
+++ b/outputs/Block2_First_Second_Exam_Progression_v12.xlsx
@@ -719,7 +719,7 @@
         <v>0.01862500000000003</v>
       </c>
       <c r="H6">
-        <v>0.002187908649066761</v>
+        <v>0.002187908649066816</v>
       </c>
       <c r="I6">
         <v>0.005372069085689518</v>
@@ -740,7 +740,7 @@
         <v>0.0172500000000001</v>
       </c>
       <c r="O6">
-        <v>0.0008129086490668291</v>
+        <v>0.0008129086490668846</v>
       </c>
       <c r="P6" t="b">
         <v>1</v>
